--- a/backend/uploads/plantillas/plantilla-liquidaciones.xlsx
+++ b/backend/uploads/plantillas/plantilla-liquidaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\OneDrive\Documentos\GITHUB\NHPanamericano\backend\uploads\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADF5C8C-5685-4B73-8F50-D369A6BD4642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A7C797-A13F-4963-99D7-A1CAD8C874B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{320E455E-E671-418D-AD74-D1199C5B9D2B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -66,39 +66,6 @@
     <t>Valor Total</t>
   </si>
   <si>
-    <t>HABITACION ( Incluye cuidado y manejo diario de un paciente monitoreado)</t>
-  </si>
-  <si>
-    <t>Medicinas e Insumos Quirurgico</t>
-  </si>
-  <si>
-    <t>Medicinas e Insumos Clinico</t>
-  </si>
-  <si>
-    <t>Laboratorio</t>
-  </si>
-  <si>
-    <t>Derecho de Sala</t>
-  </si>
-  <si>
-    <t>Anestesia</t>
-  </si>
-  <si>
-    <t>Honorarios Medicos Traumatologia</t>
-  </si>
-  <si>
-    <t>Tac de Craneo</t>
-  </si>
-  <si>
-    <t>Tac de Columna Lumbar</t>
-  </si>
-  <si>
-    <t>Eco Abdomen Superior</t>
-  </si>
-  <si>
-    <t>Emergencia</t>
-  </si>
-  <si>
     <t>Subtotal</t>
   </si>
   <si>
@@ -106,12 +73,6 @@
   </si>
   <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Honorarios Medicos Internista</t>
-  </si>
-  <si>
-    <t>Rayos X ap + lateral Rodilla</t>
   </si>
   <si>
     <t xml:space="preserve">Medico Tratante: </t>
@@ -202,7 +163,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -244,7 +206,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
@@ -274,48 +236,47 @@
     <xf numFmtId="12" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -778,7 +739,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10EF6C4F-467A-4E8E-913D-948852CFCF76}">
   <sheetPr codeName="Hoja8"/>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
@@ -794,39 +755,39 @@
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -842,7 +803,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
@@ -852,7 +813,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
@@ -861,7 +822,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="9"/>
@@ -869,9 +830,9 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="31"/>
+        <v>16</v>
+      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="9" t="s">
         <v>0</v>
       </c>
@@ -879,7 +840,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="9"/>
@@ -897,146 +858,240 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="14"/>
-      <c r="B15" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="24"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="17"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="24"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="17"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="24"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="21"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="24"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="21"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="24"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="17"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="24"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="23"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="14"/>
-      <c r="B22" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="24"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="17"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="17"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="17"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="24"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="17"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="18"/>
-      <c r="B27" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="17"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="24"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="17"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="24"/>
       <c r="F28" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="24"/>
-      <c r="B29" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="26"/>
-    </row>
-    <row r="30" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="27"/>
-    </row>
-    <row r="31" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B31" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="27"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D33" s="30"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="16"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="24"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="16"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="24"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="27"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="24"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="27"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="24"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="27"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="24"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="27"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="24"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="27"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="24"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="27"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="24"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="27"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="24"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="27"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="24"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="27"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="24"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="27"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="24"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="27"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="24"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="27"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="24"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="27"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="24"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="27"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="24"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="27"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="24"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="27"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="24"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="27"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="24"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="27"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="24"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="27"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="24"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B50" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="29"/>
+      <c r="D50" s="30"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B51" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="28"/>
+      <c r="D51" s="30"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B52" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="28"/>
+      <c r="D52" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="4">
